--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484107_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484107_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6711</v>
+        <v>2.5691</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9131</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>1.758</v>
@@ -610,10 +610,10 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4195</v>
+        <v>0.3174</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1418</v>
+        <v>0.0398</v>
       </c>
       <c r="U2" t="n">
         <v>0.2777</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0968</v>
+        <v>1.8661</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7904</v>
+        <v>2.0988</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3065</v>
+        <v>-0.2327</v>
       </c>
       <c r="G3" t="n">
-        <v>2.271</v>
+        <v>-0.219</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5266</v>
+        <v>0.1762</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2556</v>
+        <v>-0.3951</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7583</v>
+        <v>0.7057</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6382</v>
+        <v>0.7057</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.8799</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4872</v>
+        <v>-0.9246</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1116</v>
+        <v>-0.5295</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3756</v>
+        <v>-0.3951</v>
       </c>
       <c r="P3" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1822</v>
+        <v>-0.3968</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9078</v>
+        <v>0.6802</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1144</v>
+        <v>0.3175</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7934</v>
+        <v>0.3627</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.2804</v>
+        <v>1.2065</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.9001</v>
+        <v>1.4724</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3803</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9783</v>
+        <v>0.5523</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0988</v>
+        <v>-0.4737</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1205</v>
+        <v>1.0259</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.219</v>
+        <v>2.271</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1762</v>
+        <v>4.5266</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3951</v>
+        <v>-2.2556</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7057</v>
+        <v>2.7583</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7057</v>
+        <v>4.6382</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1.8799</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9246</v>
+        <v>-0.4872</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5295</v>
+        <v>-0.1116</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3951</v>
+        <v>-0.3756</v>
       </c>
       <c r="P4" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3968</v>
+        <v>-2.1822</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7924</v>
+        <v>1.3632</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3175</v>
+        <v>0.8504</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4749</v>
+        <v>0.5128</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2065</v>
+        <v>-3.2804</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4724</v>
+        <v>-1.9001</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-1.3803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0526</v>
+        <v>-0.4559</v>
       </c>
       <c r="E5" t="n">
-        <v>2.14</v>
+        <v>-1.499</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.1926</v>
+        <v>1.0431</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3049</v>
+        <v>4.3935</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0756</v>
+        <v>5.1359</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2294</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6901</v>
+        <v>3.6759</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5981</v>
+        <v>5.1115</v>
       </c>
       <c r="L5" t="n">
-        <v>1.092</v>
+        <v>-1.4356</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.995</v>
+        <v>0.7176</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6736</v>
+        <v>0.0244</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3214</v>
+        <v>0.6932</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9919</v>
+        <v>-2.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5871</v>
+        <v>-5.158</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5952</v>
+        <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1847</v>
+        <v>0.6745</v>
       </c>
       <c r="T5" t="n">
-        <v>0.771</v>
+        <v>-0.0169</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4137</v>
+        <v>0.6914</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9405</v>
+        <v>-2.9449</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-2.9449</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SERRA CASTILLO</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1329</v>
+        <v>-0.9903</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0233</v>
+        <v>2.2023</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1562</v>
+        <v>-3.1926</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9662</v>
+        <v>-0.3049</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3377</v>
+        <v>-0.0756</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6285</v>
+        <v>-0.2294</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.912</v>
+        <v>2.6901</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3279</v>
+        <v>1.5981</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2399</v>
+        <v>1.092</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0542</v>
+        <v>-2.995</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6655</v>
+        <v>-1.6736</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3886</v>
+        <v>-1.3214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.5871</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8763</v>
+        <v>1.247</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9353</v>
+        <v>0.8333</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.059</v>
+        <v>0.4137</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4398</v>
+        <v>-0.9405</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4398</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>J. SERRA CASTILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5385</v>
+        <v>-1.689</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5816</v>
+        <v>-0.5889</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0431</v>
+        <v>-1.1001</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3935</v>
+        <v>-1.9662</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1359</v>
+        <v>-0.3377</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-1.6285</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6759</v>
+        <v>-0.912</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1115</v>
+        <v>0.3279</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4356</v>
+        <v>-1.2399</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7176</v>
+        <v>-1.0542</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0244</v>
+        <v>-0.6655</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6932</v>
+        <v>-0.3886</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.579</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.158</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.579</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4081</v>
+        <v>0.3203</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0995</v>
+        <v>0.3231</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6914</v>
+        <v>-0.0029</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.9449</v>
+        <v>-0.4398</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.9449</v>
+        <v>-0.4398</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8025</v>
+        <v>-1.7019</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7118</v>
+        <v>-2.7515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9093</v>
+        <v>1.0496</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5295</v>
@@ -1078,13 +1078,13 @@
         <v>2.7774</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0912</v>
+        <v>1.1918</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8901</v>
+        <v>0.8504</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2011</v>
+        <v>0.3414</v>
       </c>
       <c r="V8" t="n">
         <v>0.4294</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7529</v>
+        <v>-2.0744</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2603</v>
+        <v>-1.7502</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4926</v>
+        <v>-0.3242</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7356</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3979</v>
+        <v>0.2806</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3004</v>
+        <v>0.2098</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0975</v>
+        <v>0.0708</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4129</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2864</v>
+        <v>-3.6998</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9685</v>
+        <v>-2.6625</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3178</v>
+        <v>-1.0373</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0186</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.1105</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6121</v>
+        <v>-0.306</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.1955</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1738</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8815</v>
+        <v>-4.7514</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8908</v>
+        <v>-1.7888</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9907</v>
+        <v>-2.9626</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6244</v>
@@ -1312,13 +1312,13 @@
         <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1151</v>
+        <v>0.2452</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1928</v>
+        <v>0.2948</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0496</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3803</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9463</v>
+        <v>-4.9605</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9108</v>
+        <v>-4.6444</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0355</v>
+        <v>-0.316</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0804</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.3859</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6463</v>
+        <v>0.9127</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7537</v>
+        <v>0.4732</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4724</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.6474</v>
+        <v>-15.3357</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.3582</v>
+        <v>-11.0469</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.289</v>
+        <v>-4.2889</v>
       </c>
       <c r="G13" t="n">
         <v>-7.4824</v>
@@ -1468,10 +1468,10 @@
         <v>14.879</v>
       </c>
       <c r="S13" t="n">
-        <v>7.283900000000001</v>
+        <v>7.595599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9972</v>
+        <v>4.3089</v>
       </c>
       <c r="U13" t="n">
         <v>3.2867</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9472</v>
+        <v>7.4456</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9514</v>
+        <v>4.7474</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9957</v>
+        <v>2.6982</v>
       </c>
       <c r="G14" t="n">
         <v>0.4845</v>
@@ -1546,13 +1546,13 @@
         <v>3.1741</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2606</v>
+        <v>-0.241</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0511</v>
+        <v>-0.1529</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2094</v>
+        <v>-0.0881</v>
       </c>
       <c r="V14" t="n">
         <v>4.0279</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1097</v>
+        <v>4.1539</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0206</v>
+        <v>1.8165</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0891</v>
+        <v>2.3374</v>
       </c>
       <c r="G15" t="n">
         <v>4.1038</v>
@@ -1624,13 +1624,13 @@
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8038</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3797</v>
+        <v>-0.5837</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4241</v>
+        <v>-0.1758</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2267</v>
+        <v>3.9511</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3315</v>
+        <v>2.5356</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8952</v>
+        <v>1.4155</v>
       </c>
       <c r="G16" t="n">
         <v>3.7435</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0135</v>
+        <v>-0.2891</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.39</v>
+        <v>0.1303</v>
       </c>
       <c r="V16" t="n">
         <v>2.6789</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5681</v>
+        <v>2.3343</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.0327</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0253</v>
+        <v>2.3016</v>
       </c>
       <c r="G17" t="n">
         <v>2.8143</v>
@@ -1780,13 +1780,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5753</v>
+        <v>-0.8092</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2382</v>
+        <v>-0.272</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8135</v>
+        <v>-0.5372</v>
       </c>
       <c r="V17" t="n">
         <v>-0.266</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4643</v>
+        <v>2.3002</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4951</v>
+        <v>1.087</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9692</v>
+        <v>1.2132</v>
       </c>
       <c r="G18" t="n">
         <v>0.8741</v>
@@ -1858,13 +1858,13 @@
         <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5028</v>
+        <v>0.3387</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6178</v>
+        <v>0.2097</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1151</v>
+        <v>0.1289</v>
       </c>
       <c r="V18" t="n">
         <v>1.881</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5952</v>
+        <v>0.8154</v>
       </c>
       <c r="E19" t="n">
         <v>0.203</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3922</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0.5391</v>
@@ -1936,13 +1936,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3407</v>
+        <v>-0.1205</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.216</v>
+        <v>0.0042</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5819</v>
+        <v>-0.1117</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5091</v>
+        <v>-1.203</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9273</v>
+        <v>1.0914</v>
       </c>
       <c r="G20" t="n">
         <v>-1.037</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7352</v>
+        <v>-0.265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2494</v>
+        <v>0.0567</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4858</v>
+        <v>-0.3217</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6034</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3044</v>
+        <v>-0.6105</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.299</v>
+        <v>-0.1672</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5657</v>
@@ -2092,13 +2092,13 @@
         <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0539</v>
+        <v>-0.2282</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1982</v>
+        <v>-0.5043</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1444</v>
+        <v>0.2762</v>
       </c>
       <c r="V21" t="n">
         <v>3.6194</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.748</v>
+        <v>-0.8274</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2018</v>
+        <v>-1.7301</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4538</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7393</v>
+        <v>-1.2136</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8169</v>
+        <v>-1.6178</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5562</v>
+        <v>0.4042</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3561</v>
+        <v>-0.4067</v>
       </c>
       <c r="K22" t="n">
-        <v>0.711</v>
+        <v>0.9837</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6451</v>
+        <v>-1.3903</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3832</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5278</v>
+        <v>-2.6015</v>
       </c>
       <c r="O22" t="n">
-        <v>1.911</v>
+        <v>1.7945</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1822</v>
+        <v>2.7774</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7855</v>
+        <v>2.7774</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8371</v>
+        <v>-1.1847</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1222</v>
+        <v>-0.9861</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7149</v>
+        <v>-0.1985</v>
       </c>
       <c r="V22" t="n">
-        <v>0.532</v>
+        <v>-1.2065</v>
       </c>
       <c r="W22" t="n">
-        <v>0.532</v>
+        <v>-0.3373</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3306</v>
+        <v>-0.9156</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2402</v>
+        <v>-2.5897</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.09039999999999999</v>
+        <v>1.674</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2136</v>
+        <v>1.7393</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6178</v>
+        <v>-0.8169</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4042</v>
+        <v>2.5562</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4067</v>
+        <v>1.3561</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9837</v>
+        <v>0.711</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3903</v>
+        <v>0.6451</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0.3832</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.6015</v>
+        <v>-1.5278</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7945</v>
+        <v>1.911</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7774</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q23" t="n">
+        <v>-3.9677</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.0047</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.4947</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.7774</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-2.6879</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-1.4963</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-1.1916</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-1.2065</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-0.3373</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-0.8692</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.6473</v>
+        <v>18.36809999999999</v>
       </c>
       <c r="E24" t="n">
         <v>4.2889</v>
       </c>
       <c r="F24" t="n">
-        <v>11.3584</v>
+        <v>14.0792</v>
       </c>
       <c r="G24" t="n">
-        <v>7.482300000000002</v>
+        <v>7.4823</v>
       </c>
       <c r="H24" t="n">
         <v>-9.425000000000001</v>
@@ -2302,7 +2302,7 @@
         <v>8.0672</v>
       </c>
       <c r="K24" t="n">
-        <v>4.213699999999999</v>
+        <v>4.2137</v>
       </c>
       <c r="L24" t="n">
         <v>3.8537</v>
@@ -2326,13 +2326,13 @@
         <v>17.8547</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.284</v>
+        <v>-4.5633</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.2869</v>
+        <v>-3.2867</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.9972</v>
+        <v>-1.2764</v>
       </c>
       <c r="V24" t="n">
         <v>12.4732</v>
